--- a/artfynd/A 57059-2024 artfynd.xlsx
+++ b/artfynd/A 57059-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1511220</v>
+        <v>112253193</v>
       </c>
       <c r="B2" t="n">
-        <v>89793</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eldsjömyran-Flakamyran, Ås lm</t>
+          <t>Eldsjömyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587241.3435012</v>
+        <v>587010</v>
       </c>
       <c r="R2" t="n">
-        <v>7106437.007819635</v>
+        <v>7106380</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-10-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inv reviderad msp</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,55 +757,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112253149</v>
+        <v>112253147</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,7 +817,7 @@
         <v>587127</v>
       </c>
       <c r="R3" t="n">
-        <v>7106323</v>
+        <v>7106324</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -898,56 +877,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112253048</v>
+        <v>1511220</v>
       </c>
       <c r="B4" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eldsjömyran, Ås lm</t>
+          <t>Eldsjömyran-Flakamyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587296</v>
+        <v>587241</v>
       </c>
       <c r="R4" t="n">
-        <v>7106305</v>
+        <v>7106437</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +942,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2005-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2005-10-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inv reviderad msp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,56 +961,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112253033</v>
+        <v>112253012</v>
       </c>
       <c r="B5" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587204</v>
+        <v>587091</v>
       </c>
       <c r="R5" t="n">
-        <v>7106454</v>
+        <v>7106666</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112253138</v>
+        <v>112253095</v>
       </c>
       <c r="B6" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587127</v>
+        <v>587180</v>
       </c>
       <c r="R6" t="n">
-        <v>7106323</v>
+        <v>7106253</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112253095</v>
+        <v>112253210</v>
       </c>
       <c r="B7" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587180</v>
+        <v>586996</v>
       </c>
       <c r="R7" t="n">
-        <v>7106253</v>
+        <v>7106399</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112253147</v>
+        <v>112253048</v>
       </c>
       <c r="B8" t="n">
-        <v>78753</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587127</v>
+        <v>587296</v>
       </c>
       <c r="R8" t="n">
-        <v>7106323</v>
+        <v>7106306</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,15 +1383,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112253012</v>
+        <v>112253138</v>
       </c>
       <c r="B9" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1394,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587092</v>
+        <v>587127</v>
       </c>
       <c r="R9" t="n">
-        <v>7106666</v>
+        <v>7106324</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1531,6 +1481,107 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112253149</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Eldsjömyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>587127</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7106324</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57059-2024 artfynd.xlsx
+++ b/artfynd/A 57059-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253193</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1511220</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253012</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253210</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253048</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253138</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,8 +1627,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253149</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>